--- a/Result/profitability/6246.xlsx
+++ b/Result/profitability/6246.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.98</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.14875</v>
+        <v>-0.03250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>9.902499999999998</v>
+        <v>9.914999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.86</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.11125</v>
+        <v>-0.20125</v>
       </c>
       <c r="N3" t="n">
-        <v>8.108749999999999</v>
+        <v>7.923749999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N4" t="n">
-        <v>7.15625</v>
+        <v>7.1225</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.85</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2275</v>
+        <v>-0.30875</v>
       </c>
       <c r="N5" t="n">
-        <v>6.352499999999999</v>
+        <v>6.165</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.48</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="N6" t="n">
-        <v>4.979999999999999</v>
+        <v>4.76875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.21</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.305</v>
+        <v>-0.4812500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>5.4725</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.34625</v>
+        <v>-0.29</v>
       </c>
       <c r="N8" t="n">
-        <v>6.652499999999999</v>
+        <v>7.042499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01999999999999998</v>
+        <v>0.02</v>
       </c>
       <c r="N11" t="n">
         <v>11.4825</v>
@@ -1899,7 +1899,7 @@
         <v>0.18</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03999999999999998</v>
+        <v>0.03999999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>13.4825</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6246</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>344</v>
+      </c>
+      <c r="D75" t="n">
+        <v>308</v>
+      </c>
+      <c r="E75" t="n">
+        <v>37</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.05500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.1075</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.661764705882353</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.119999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4159999999999999</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.547619047619048</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1237623762376238</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
